--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Player Name</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>Ko2l</t>
+  </si>
+  <si>
+    <t>pppppoppppppp</t>
+  </si>
+  <si>
+    <t>Hek</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Okd</t>
   </si>
 </sst>
 </file>
@@ -95,7 +107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -202,6 +214,38 @@
         <v>2.0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Player Name</t>
   </si>
@@ -63,6 +63,18 @@
   </si>
   <si>
     <t>Okd</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>dfasf</t>
   </si>
 </sst>
 </file>
@@ -107,7 +119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -246,6 +258,38 @@
         <v>3.0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Player Name</t>
   </si>
@@ -75,6 +75,30 @@
   </si>
   <si>
     <t>dfasf</t>
+  </si>
+  <si>
+    <t>Kolem</t>
+  </si>
+  <si>
+    <t>kjjaksd</t>
+  </si>
+  <si>
+    <t>pkl</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>ddkadke</t>
+  </si>
+  <si>
+    <t>jj</t>
+  </si>
+  <si>
+    <t>fsdf</t>
+  </si>
+  <si>
+    <t>lol</t>
   </si>
 </sst>
 </file>
@@ -119,7 +143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -290,6 +314,70 @@
         <v>4.0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Player Name</t>
   </si>
@@ -99,6 +99,63 @@
   </si>
   <si>
     <t>lol</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>lk</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>asdw</t>
+  </si>
+  <si>
+    <t>asd2</t>
+  </si>
+  <si>
+    <t>ad13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>f123</t>
+  </si>
+  <si>
+    <t>3414</t>
+  </si>
+  <si>
+    <t>jom</t>
+  </si>
+  <si>
+    <t>e1e13</t>
+  </si>
+  <si>
+    <t>e3</t>
+  </si>
+  <si>
+    <t>de2</t>
+  </si>
+  <si>
+    <t>ee3</t>
+  </si>
+  <si>
+    <t>e2</t>
+  </si>
+  <si>
+    <t>ad</t>
   </si>
 </sst>
 </file>
@@ -143,7 +200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -378,6 +435,190 @@
         <v>19.0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" t="n">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" t="n">
+        <v>-1.821123914E9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3.09230423E8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Player Name</t>
   </si>
@@ -156,6 +156,33 @@
   </si>
   <si>
     <t>ad</t>
+  </si>
+  <si>
+    <t>e13</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>kmkl</t>
+  </si>
+  <si>
+    <t>kk</t>
+  </si>
+  <si>
+    <t>dad</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>fd13r1</t>
+  </si>
+  <si>
+    <t>d3</t>
   </si>
 </sst>
 </file>
@@ -200,7 +227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -619,6 +646,150 @@
         <v>8.0</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>51</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>55</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>Player Name</t>
   </si>
@@ -183,6 +183,18 @@
   </si>
   <si>
     <t>d3</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>d33</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>fe3</t>
   </si>
 </sst>
 </file>
@@ -227,7 +239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -790,6 +802,38 @@
         <v>1.0</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>57</v>
+      </c>
+      <c r="B71" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
   <si>
     <t>Player Name</t>
   </si>
@@ -195,6 +195,39 @@
   </si>
   <si>
     <t>fe3</t>
+  </si>
+  <si>
+    <t>ae</t>
+  </si>
+  <si>
+    <t>ed31</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>e4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>e33</t>
+  </si>
+  <si>
+    <t>e32</t>
+  </si>
+  <si>
+    <t>de3</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>d3d</t>
   </si>
 </sst>
 </file>
@@ -239,7 +272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -834,6 +867,126 @@
         <v>2.0</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" t="n">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>56</v>
+      </c>
+      <c r="B81" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>68</v>
+      </c>
+      <c r="B86" t="n">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" t="n">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89" t="n">
+        <v>44.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
   <si>
     <t>Player Name</t>
   </si>
@@ -228,6 +228,42 @@
   </si>
   <si>
     <t>d3d</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>de13</t>
+  </si>
+  <si>
+    <t>3f1</t>
+  </si>
+  <si>
+    <t>3r4</t>
+  </si>
+  <si>
+    <t>d31d3</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>3e1</t>
+  </si>
+  <si>
+    <t>d13</t>
+  </si>
+  <si>
+    <t>sqaq</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>ded</t>
   </si>
 </sst>
 </file>
@@ -272,7 +308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -987,6 +1023,230 @@
         <v>44.0</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>46</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>73</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>56</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>56</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>77</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>57</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>78</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>56</v>
+      </c>
+      <c r="B108" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>80</v>
+      </c>
+      <c r="B110" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>56</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>81</v>
+      </c>
+      <c r="B114" t="n">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>82</v>
+      </c>
+      <c r="B115" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>56</v>
+      </c>
+      <c r="B116" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>Player Name</t>
   </si>
@@ -264,6 +264,18 @@
   </si>
   <si>
     <t>ded</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>s31</t>
+  </si>
+  <si>
+    <t>f4</t>
+  </si>
+  <si>
+    <t>31e</t>
   </si>
 </sst>
 </file>
@@ -308,7 +320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1259,54 @@
         <v>8.0</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>85</v>
+      </c>
+      <c r="B119" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>43</v>
+      </c>
+      <c r="B120" t="n">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>86</v>
+      </c>
+      <c r="B121" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>87</v>
+      </c>
+      <c r="B122" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>56</v>
+      </c>
+      <c r="B123" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
   <si>
     <t>Player Name</t>
   </si>
@@ -320,7 +320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1307,6 +1307,14 @@
         <v>7.0</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CW2013/local_leaderboard.xlsx
+++ b/CW2013/local_leaderboard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="107">
   <si>
     <t>Player Name</t>
   </si>
@@ -321,6 +321,18 @@
   </si>
   <si>
     <t>f4f</t>
+  </si>
+  <si>
+    <t>jjr</t>
+  </si>
+  <si>
+    <t>kkk</t>
+  </si>
+  <si>
+    <t>jhkjh</t>
+  </si>
+  <si>
+    <t>kj</t>
   </si>
 </sst>
 </file>
@@ -365,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B175"/>
+  <dimension ref="A1:B179"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1780,38 @@
         <v>3.0</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>103</v>
+      </c>
+      <c r="B176" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>104</v>
+      </c>
+      <c r="B177" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>105</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>106</v>
+      </c>
+      <c r="B179" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
